--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1808,6 +1808,1787 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130043399</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92058</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>734868</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7088213</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130043382</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>735005</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7088414</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130043383</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>734964</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7088319</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130043401</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91625</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>734997</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7088331</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130043392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>734854</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7088230</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130043402</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>734867</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7088223</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130043393</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>734831</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7088297</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130043398</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92058</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>734964</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7088306</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130043390</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>734995</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7088336</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130043387</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>735005</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7088424</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130043389</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>734873</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7088242</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130043388</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>734887</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7088244</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130043386</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>734874</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7088317</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130043391</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>734960</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7088313</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130043396</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80096</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>734758</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7088019</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130043385</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>734854</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7088318</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130043395</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>734739</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7088028</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130043384</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hjåggsjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>734823</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7088271</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>130043399</v>
       </c>
       <c r="B12" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>130043401</v>
       </c>
       <c r="B15" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>130043392</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130043402</v>
+        <v>130043393</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,16 +2328,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2346,24 +2346,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734867</v>
+        <v>734831</v>
       </c>
       <c r="R17" t="n">
-        <v>7088223</v>
+        <v>7088297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,11 +2388,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043393</v>
+        <v>130043402</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,16 +2425,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2456,16 +2443,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734831</v>
+        <v>734867</v>
       </c>
       <c r="R18" t="n">
-        <v>7088297</v>
+        <v>7088223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,6 +2493,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2527,7 @@
         <v>130043398</v>
       </c>
       <c r="B19" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>130043390</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043387</v>
+        <v>130043389</v>
       </c>
       <c r="B21" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735005</v>
+        <v>734873</v>
       </c>
       <c r="R21" t="n">
-        <v>7088424</v>
+        <v>7088242</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043389</v>
+        <v>130043387</v>
       </c>
       <c r="B22" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734873</v>
+        <v>735005</v>
       </c>
       <c r="R22" t="n">
-        <v>7088242</v>
+        <v>7088424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
         <v>130043388</v>
       </c>
       <c r="B23" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>130043386</v>
       </c>
       <c r="B24" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>130043391</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>80096</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R26" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B27" t="n">
-        <v>91569</v>
+        <v>80097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R27" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
         <v>130043384</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3589,6 +3589,1373 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130068986</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>735026</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7088427</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130068992</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>734725</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7088016</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130068988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>734966</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7088329</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130043975</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91606</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>734874</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7088263</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130068989</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>734956</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7088332</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130043974</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>734870</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7088268</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130068985</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91624</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>734836</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7088304</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130043981</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>734758</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7088008</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130043979</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92059</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>734884</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7088266</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130043977</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>734812</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7088001</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130043973</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>734901</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7088302</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130068987</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>735001</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7088321</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130068991</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>734748</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7088007</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130068990</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hjåggsjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>734918</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7088299</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rebecka Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>130043399</v>
       </c>
       <c r="B12" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>130043401</v>
       </c>
       <c r="B15" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>130043392</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>130043398</v>
       </c>
       <c r="B19" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>130043390</v>
       </c>
       <c r="B20" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>130043389</v>
       </c>
       <c r="B21" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>130043387</v>
       </c>
       <c r="B22" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>130043388</v>
       </c>
       <c r="B23" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>130043386</v>
       </c>
       <c r="B24" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>130043391</v>
       </c>
       <c r="B25" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>80098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R26" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B27" t="n">
-        <v>80097</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R27" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
         <v>130043384</v>
       </c>
       <c r="B29" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130068986</v>
+        <v>130068992</v>
       </c>
       <c r="B30" t="n">
         <v>79089</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735026</v>
+        <v>734725</v>
       </c>
       <c r="R30" t="n">
-        <v>7088427</v>
+        <v>7088016</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130068992</v>
+        <v>130068986</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>734725</v>
+        <v>735026</v>
       </c>
       <c r="R31" t="n">
-        <v>7088016</v>
+        <v>7088427</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3885,7 +3885,7 @@
         <v>130043975</v>
       </c>
       <c r="B33" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>130043974</v>
       </c>
       <c r="B35" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130068985</v>
       </c>
       <c r="B36" t="n">
-        <v>91624</v>
+        <v>91637</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>130043981</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130043979</v>
       </c>
       <c r="B38" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,32 +4569,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130043973</v>
+        <v>130068987</v>
       </c>
       <c r="B40" t="n">
-        <v>91570</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734901</v>
+        <v>735001</v>
       </c>
       <c r="R40" t="n">
-        <v>7088302</v>
+        <v>7088321</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4648,26 +4648,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130068987</v>
+        <v>130068991</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4702,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735001</v>
+        <v>734748</v>
       </c>
       <c r="R41" t="n">
-        <v>7088321</v>
+        <v>7088007</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4764,32 +4763,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130068991</v>
+        <v>130043973</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>91587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4799,13 +4798,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734748</v>
+        <v>734901</v>
       </c>
       <c r="R42" t="n">
-        <v>7088007</v>
+        <v>7088302</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4843,18 +4842,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>91639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R16" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043392</v>
+        <v>130043393</v>
       </c>
       <c r="B18" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734854</v>
+        <v>734831</v>
       </c>
       <c r="R18" t="n">
-        <v>7088230</v>
+        <v>7088297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043392</v>
+        <v>130043393</v>
       </c>
       <c r="B16" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734854</v>
+        <v>734831</v>
       </c>
       <c r="R16" t="n">
-        <v>7088230</v>
+        <v>7088297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>91639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R18" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043389</v>
+        <v>130043387</v>
       </c>
       <c r="B20" t="n">
         <v>91603</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734873</v>
+        <v>735005</v>
       </c>
       <c r="R20" t="n">
-        <v>7088242</v>
+        <v>7088424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043387</v>
+        <v>130043390</v>
       </c>
       <c r="B21" t="n">
-        <v>91603</v>
+        <v>91639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735005</v>
+        <v>734995</v>
       </c>
       <c r="R21" t="n">
-        <v>7088424</v>
+        <v>7088336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043390</v>
+        <v>130043389</v>
       </c>
       <c r="B22" t="n">
-        <v>91639</v>
+        <v>91603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734995</v>
+        <v>734873</v>
       </c>
       <c r="R22" t="n">
-        <v>7088336</v>
+        <v>7088242</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>91603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R26" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B27" t="n">
-        <v>91603</v>
+        <v>80104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R27" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130068989</v>
+        <v>130043975</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734956</v>
+        <v>734874</v>
       </c>
       <c r="R33" t="n">
-        <v>7088332</v>
+        <v>7088263</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3967,22 +3967,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130043975</v>
+        <v>130068989</v>
       </c>
       <c r="B34" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4014,13 +4014,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734874</v>
+        <v>734956</v>
       </c>
       <c r="R34" t="n">
-        <v>7088263</v>
+        <v>7088332</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,12 +4064,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>130043399</v>
       </c>
       <c r="B12" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>130043401</v>
       </c>
       <c r="B15" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R16" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130043402</v>
+        <v>130043393</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,16 +2328,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2346,24 +2346,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734867</v>
+        <v>734831</v>
       </c>
       <c r="R17" t="n">
-        <v>7088223</v>
+        <v>7088297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,11 +2388,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043392</v>
+        <v>130043402</v>
       </c>
       <c r="B18" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,34 +2425,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734854</v>
+        <v>734867</v>
       </c>
       <c r="R18" t="n">
-        <v>7088230</v>
+        <v>7088223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,6 +2493,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2527,7 @@
         <v>130043398</v>
       </c>
       <c r="B19" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043387</v>
+        <v>130043389</v>
       </c>
       <c r="B20" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735005</v>
+        <v>734873</v>
       </c>
       <c r="R20" t="n">
-        <v>7088424</v>
+        <v>7088242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043390</v>
+        <v>130043387</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>91605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>734995</v>
+        <v>735005</v>
       </c>
       <c r="R21" t="n">
-        <v>7088336</v>
+        <v>7088424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043389</v>
+        <v>130043390</v>
       </c>
       <c r="B22" t="n">
-        <v>91603</v>
+        <v>91641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734873</v>
+        <v>734995</v>
       </c>
       <c r="R22" t="n">
-        <v>7088242</v>
+        <v>7088336</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
         <v>130043388</v>
       </c>
       <c r="B23" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>130043386</v>
       </c>
       <c r="B24" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>130043391</v>
       </c>
       <c r="B25" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130043384</v>
       </c>
       <c r="B29" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>130043975</v>
       </c>
       <c r="B33" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>130043974</v>
       </c>
       <c r="B35" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130068985</v>
       </c>
       <c r="B36" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130043979</v>
       </c>
       <c r="B38" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>130043973</v>
       </c>
       <c r="B40" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>130043399</v>
       </c>
       <c r="B12" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130043382</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>130043383</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>130043401</v>
       </c>
       <c r="B15" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043392</v>
+        <v>130043402</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,34 +2231,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734854</v>
+        <v>734867</v>
       </c>
       <c r="R16" t="n">
-        <v>7088230</v>
+        <v>7088223</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,6 +2299,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2352,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R17" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043402</v>
+        <v>130043393</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,16 +2438,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2443,24 +2456,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734867</v>
+        <v>734831</v>
       </c>
       <c r="R18" t="n">
-        <v>7088223</v>
+        <v>7088297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,11 +2498,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2527,7 @@
         <v>130043398</v>
       </c>
       <c r="B19" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>130043389</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043387</v>
+        <v>130043390</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735005</v>
+        <v>734995</v>
       </c>
       <c r="R21" t="n">
-        <v>7088424</v>
+        <v>7088336</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043390</v>
+        <v>130043387</v>
       </c>
       <c r="B22" t="n">
-        <v>91641</v>
+        <v>91692</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734995</v>
+        <v>735005</v>
       </c>
       <c r="R22" t="n">
-        <v>7088336</v>
+        <v>7088424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130043388</v>
+        <v>130043386</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>734887</v>
+        <v>734874</v>
       </c>
       <c r="R23" t="n">
-        <v>7088244</v>
+        <v>7088317</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130043386</v>
+        <v>130043388</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>734874</v>
+        <v>734887</v>
       </c>
       <c r="R24" t="n">
-        <v>7088317</v>
+        <v>7088244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
         <v>130043391</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>130043396</v>
       </c>
       <c r="B27" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>130043395</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130043384</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>130068992</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>130068986</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>130068988</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>130043975</v>
       </c>
       <c r="B33" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>130068989</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>130043974</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130068985</v>
       </c>
       <c r="B36" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>130043981</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>130043979</v>
       </c>
       <c r="B38" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>130043977</v>
       </c>
       <c r="B39" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>130043973</v>
       </c>
       <c r="B40" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130068987</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>130068991</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>130068990</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B26" t="n">
-        <v>91692</v>
+        <v>80189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R26" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B27" t="n">
-        <v>80189</v>
+        <v>91692</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R27" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130068992</v>
+        <v>130068986</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>734725</v>
+        <v>735026</v>
       </c>
       <c r="R30" t="n">
-        <v>7088016</v>
+        <v>7088427</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130068986</v>
+        <v>130068992</v>
       </c>
       <c r="B31" t="n">
         <v>79180</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735026</v>
+        <v>734725</v>
       </c>
       <c r="R31" t="n">
-        <v>7088427</v>
+        <v>7088016</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>80189</v>
+        <v>91692</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R26" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B27" t="n">
-        <v>91692</v>
+        <v>80189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R27" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043402</v>
+        <v>130043393</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2249,24 +2249,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734867</v>
+        <v>734831</v>
       </c>
       <c r="R16" t="n">
-        <v>7088223</v>
+        <v>7088297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,11 +2291,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130043392</v>
+        <v>130043402</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2341,34 +2328,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734854</v>
+        <v>734867</v>
       </c>
       <c r="R17" t="n">
-        <v>7088230</v>
+        <v>7088223</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,6 +2396,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R18" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043389</v>
+        <v>130043390</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734873</v>
+        <v>734995</v>
       </c>
       <c r="R20" t="n">
-        <v>7088242</v>
+        <v>7088336</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043390</v>
+        <v>130043389</v>
       </c>
       <c r="B21" t="n">
-        <v>91728</v>
+        <v>91692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>734995</v>
+        <v>734873</v>
       </c>
       <c r="R21" t="n">
-        <v>7088336</v>
+        <v>7088242</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130043386</v>
+        <v>130043388</v>
       </c>
       <c r="B23" t="n">
         <v>91692</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>734874</v>
+        <v>734887</v>
       </c>
       <c r="R23" t="n">
-        <v>7088317</v>
+        <v>7088244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130043388</v>
+        <v>130043386</v>
       </c>
       <c r="B24" t="n">
         <v>91692</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>734887</v>
+        <v>734874</v>
       </c>
       <c r="R24" t="n">
-        <v>7088244</v>
+        <v>7088317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B26" t="n">
-        <v>91692</v>
+        <v>80189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R26" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B27" t="n">
-        <v>80189</v>
+        <v>91692</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R27" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130068987</v>
+        <v>130068991</v>
       </c>
       <c r="B41" t="n">
         <v>79180</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735001</v>
+        <v>734748</v>
       </c>
       <c r="R41" t="n">
-        <v>7088321</v>
+        <v>7088007</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130068991</v>
+        <v>130068987</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734748</v>
+        <v>735001</v>
       </c>
       <c r="R42" t="n">
-        <v>7088007</v>
+        <v>7088321</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043390</v>
+        <v>130043389</v>
       </c>
       <c r="B20" t="n">
-        <v>91728</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734995</v>
+        <v>734873</v>
       </c>
       <c r="R20" t="n">
-        <v>7088336</v>
+        <v>7088242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043389</v>
+        <v>130043387</v>
       </c>
       <c r="B21" t="n">
         <v>91692</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>734873</v>
+        <v>735005</v>
       </c>
       <c r="R21" t="n">
-        <v>7088242</v>
+        <v>7088424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043387</v>
+        <v>130043390</v>
       </c>
       <c r="B22" t="n">
-        <v>91692</v>
+        <v>91728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735005</v>
+        <v>734995</v>
       </c>
       <c r="R22" t="n">
-        <v>7088424</v>
+        <v>7088336</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130068986</v>
+        <v>130068992</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735026</v>
+        <v>734725</v>
       </c>
       <c r="R30" t="n">
-        <v>7088427</v>
+        <v>7088016</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130068992</v>
+        <v>130068986</v>
       </c>
       <c r="B31" t="n">
         <v>79180</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>734725</v>
+        <v>735026</v>
       </c>
       <c r="R31" t="n">
-        <v>7088016</v>
+        <v>7088427</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130068991</v>
+        <v>130068987</v>
       </c>
       <c r="B41" t="n">
         <v>79180</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>734748</v>
+        <v>735001</v>
       </c>
       <c r="R41" t="n">
-        <v>7088007</v>
+        <v>7088321</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130068987</v>
+        <v>130068991</v>
       </c>
       <c r="B42" t="n">
         <v>79180</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735001</v>
+        <v>734748</v>
       </c>
       <c r="R42" t="n">
-        <v>7088321</v>
+        <v>7088007</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043393</v>
+        <v>130043392</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R16" t="n">
-        <v>7088297</v>
+        <v>7088230</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043392</v>
+        <v>130043393</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734854</v>
+        <v>734831</v>
       </c>
       <c r="R18" t="n">
-        <v>7088230</v>
+        <v>7088297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043389</v>
+        <v>130043390</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734873</v>
+        <v>734995</v>
       </c>
       <c r="R20" t="n">
-        <v>7088242</v>
+        <v>7088336</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043387</v>
+        <v>130043389</v>
       </c>
       <c r="B21" t="n">
         <v>91692</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735005</v>
+        <v>734873</v>
       </c>
       <c r="R21" t="n">
-        <v>7088424</v>
+        <v>7088242</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043390</v>
+        <v>130043387</v>
       </c>
       <c r="B22" t="n">
-        <v>91728</v>
+        <v>91692</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734995</v>
+        <v>735005</v>
       </c>
       <c r="R22" t="n">
-        <v>7088336</v>
+        <v>7088424</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043396</v>
+        <v>130043385</v>
       </c>
       <c r="B26" t="n">
-        <v>80189</v>
+        <v>91692</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734758</v>
+        <v>734854</v>
       </c>
       <c r="R26" t="n">
-        <v>7088019</v>
+        <v>7088318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043385</v>
+        <v>130043396</v>
       </c>
       <c r="B27" t="n">
-        <v>91692</v>
+        <v>80189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734854</v>
+        <v>734758</v>
       </c>
       <c r="R27" t="n">
-        <v>7088318</v>
+        <v>7088019</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -3882,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130068989</v>
+        <v>130043975</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734956</v>
+        <v>734874</v>
       </c>
       <c r="R33" t="n">
-        <v>7088332</v>
+        <v>7088263</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3967,22 +3967,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130043975</v>
+        <v>130068989</v>
       </c>
       <c r="B34" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4014,13 +4014,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734874</v>
+        <v>734956</v>
       </c>
       <c r="R34" t="n">
-        <v>7088263</v>
+        <v>7088332</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,12 +4064,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111965439</v>
+        <v>111964050</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734926</v>
+        <v>734893</v>
       </c>
       <c r="R2" t="n">
-        <v>7088234</v>
+        <v>7088354</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111964863</v>
+        <v>111964847</v>
       </c>
       <c r="B3" t="n">
-        <v>89893</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,7 +819,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734972</v>
+        <v>734973</v>
       </c>
       <c r="R3" t="n">
         <v>7088253</v>
@@ -881,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111964457</v>
+        <v>130043390</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,38 +902,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734949</v>
+        <v>734995</v>
       </c>
       <c r="R4" t="n">
-        <v>7088268</v>
+        <v>7088336</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,66 +976,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111964622</v>
+        <v>130043391</v>
       </c>
       <c r="B5" t="n">
-        <v>89993</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>734972</v>
+        <v>734960</v>
       </c>
       <c r="R5" t="n">
-        <v>7088253</v>
+        <v>7088313</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1073,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111964847</v>
+        <v>130043392</v>
       </c>
       <c r="B6" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,20 +1114,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>734972</v>
+        <v>734854</v>
       </c>
       <c r="R6" t="n">
-        <v>7088253</v>
+        <v>7088230</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,66 +1170,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111964050</v>
+        <v>130043975</v>
       </c>
       <c r="B7" t="n">
-        <v>90213</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>734893</v>
+        <v>734874</v>
       </c>
       <c r="R7" t="n">
-        <v>7088355</v>
+        <v>7088263</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1247,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,66 +1267,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111965370</v>
+        <v>130068985</v>
       </c>
       <c r="B8" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>734940</v>
+        <v>734836</v>
       </c>
       <c r="R8" t="n">
-        <v>7088232</v>
+        <v>7088304</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,22 +1344,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,27 +1364,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111964632</v>
+        <v>111964622</v>
       </c>
       <c r="B9" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1387,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,7 +1412,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>734972</v>
+        <v>734973</v>
       </c>
       <c r="R9" t="n">
         <v>7088253</v>
@@ -1579,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111964175</v>
+        <v>130043397</v>
       </c>
       <c r="B10" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,38 +1495,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>734896</v>
+        <v>735073</v>
       </c>
       <c r="R10" t="n">
-        <v>7088342</v>
+        <v>7088415</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,22 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,27 +1569,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111965883</v>
+        <v>130043398</v>
       </c>
       <c r="B11" t="n">
-        <v>55643</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,43 +1592,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kallhögen 5, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734847</v>
+        <v>734964</v>
       </c>
       <c r="R11" t="n">
-        <v>7088238</v>
+        <v>7088306</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,22 +1646,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,12 +1666,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1813,11 +1681,11 @@
         <v>130043399</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1907,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130043382</v>
+        <v>130043979</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1786,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735005</v>
+        <v>734884</v>
       </c>
       <c r="R13" t="n">
-        <v>7088414</v>
+        <v>7088266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,11 +1848,6 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2005,22 +1860,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130043383</v>
+        <v>111965370</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,45 +1883,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Kallhögen 5, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>734964</v>
+        <v>734939</v>
       </c>
       <c r="R14" t="n">
-        <v>7088319</v>
+        <v>7088232</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,17 +1938,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,56 +1968,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130043401</v>
+        <v>111964863</v>
       </c>
       <c r="B15" t="n">
-        <v>91748</v>
+        <v>92281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Kallhögen 5, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734997</v>
+        <v>734973</v>
       </c>
       <c r="R15" t="n">
-        <v>7088331</v>
+        <v>7088253</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,19 +2046,29 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2208,44 +2076,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130043392</v>
+        <v>130043384</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>734854</v>
+        <v>734823</v>
       </c>
       <c r="R16" t="n">
-        <v>7088230</v>
+        <v>7088271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130043393</v>
+        <v>130043385</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2352,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734831</v>
+        <v>734854</v>
       </c>
       <c r="R17" t="n">
-        <v>7088297</v>
+        <v>7088318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,53 +2282,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130043402</v>
+        <v>130043386</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734867</v>
+        <v>734874</v>
       </c>
       <c r="R18" t="n">
-        <v>7088223</v>
+        <v>7088317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130043398</v>
+        <v>130043387</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734964</v>
+        <v>735005</v>
       </c>
       <c r="R19" t="n">
-        <v>7088306</v>
+        <v>7088424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130043389</v>
+        <v>130043388</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734873</v>
+        <v>734887</v>
       </c>
       <c r="R20" t="n">
-        <v>7088242</v>
+        <v>7088244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2573,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130043387</v>
+        <v>130043389</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735005</v>
+        <v>734873</v>
       </c>
       <c r="R21" t="n">
-        <v>7088424</v>
+        <v>7088242</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,45 +2670,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130043390</v>
+        <v>130043973</v>
       </c>
       <c r="B22" t="n">
-        <v>91728</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>734995</v>
+        <v>734901</v>
       </c>
       <c r="R22" t="n">
-        <v>7088336</v>
+        <v>7088302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,28 +2749,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130043388</v>
+        <v>130043974</v>
       </c>
       <c r="B23" t="n">
-        <v>91692</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,14 +2799,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>734887</v>
+        <v>734870</v>
       </c>
       <c r="R23" t="n">
-        <v>7088244</v>
+        <v>7088268</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,60 +2853,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130043386</v>
+        <v>111964632</v>
       </c>
       <c r="B24" t="n">
-        <v>91692</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Kallhögen 5, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>734874</v>
+        <v>734973</v>
       </c>
       <c r="R24" t="n">
-        <v>7088317</v>
+        <v>7088253</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3074,12 +2931,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,57 +2961,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130043391</v>
+        <v>130043981</v>
       </c>
       <c r="B25" t="n">
-        <v>91728</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>734960</v>
+        <v>734758</v>
       </c>
       <c r="R25" t="n">
-        <v>7088313</v>
+        <v>7088008</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,60 +3058,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130043385</v>
+        <v>130068986</v>
       </c>
       <c r="B26" t="n">
-        <v>91692</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>734854</v>
+        <v>735026</v>
       </c>
       <c r="R26" t="n">
-        <v>7088318</v>
+        <v>7088427</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3288,60 +3155,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130043396</v>
+        <v>130068987</v>
       </c>
       <c r="B27" t="n">
-        <v>80189</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734758</v>
+        <v>735001</v>
       </c>
       <c r="R27" t="n">
-        <v>7088019</v>
+        <v>7088321</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3385,60 +3252,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130043395</v>
+        <v>130068988</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>734739</v>
+        <v>734966</v>
       </c>
       <c r="R28" t="n">
-        <v>7088028</v>
+        <v>7088329</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,60 +3349,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130043384</v>
+        <v>130068989</v>
       </c>
       <c r="B29" t="n">
-        <v>91692</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hjåggsjöbäcken, Vb</t>
+          <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>734823</v>
+        <v>734956</v>
       </c>
       <c r="R29" t="n">
-        <v>7088271</v>
+        <v>7088332</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3579,26 +3446,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130068992</v>
+        <v>130068990</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3626,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>734725</v>
+        <v>734918</v>
       </c>
       <c r="R30" t="n">
-        <v>7088016</v>
+        <v>7088299</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3688,14 +3555,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130068986</v>
+        <v>130068991</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3723,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735026</v>
+        <v>734748</v>
       </c>
       <c r="R31" t="n">
-        <v>7088427</v>
+        <v>7088007</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3785,14 +3652,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130068988</v>
+        <v>130068992</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3820,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>734966</v>
+        <v>734725</v>
       </c>
       <c r="R32" t="n">
-        <v>7088329</v>
+        <v>7088016</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3882,45 +3749,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130043975</v>
+        <v>130043396</v>
       </c>
       <c r="B33" t="n">
-        <v>91728</v>
+        <v>80336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734874</v>
+        <v>734758</v>
       </c>
       <c r="R33" t="n">
-        <v>7088263</v>
+        <v>7088019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,60 +3834,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130068989</v>
+        <v>130043393</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734956</v>
+        <v>734831</v>
       </c>
       <c r="R34" t="n">
-        <v>7088332</v>
+        <v>7088297</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,22 +3931,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130043974</v>
+        <v>130043394</v>
       </c>
       <c r="B35" t="n">
-        <v>91692</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4087,34 +3954,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734870</v>
+        <v>734798</v>
       </c>
       <c r="R35" t="n">
-        <v>7088268</v>
+        <v>7087977</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,60 +4028,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130068985</v>
+        <v>130043395</v>
       </c>
       <c r="B36" t="n">
-        <v>91742</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>734836</v>
+        <v>734739</v>
       </c>
       <c r="R36" t="n">
-        <v>7088304</v>
+        <v>7088028</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4258,57 +4125,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130043981</v>
+        <v>130043977</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hjåggsjö, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734758</v>
+        <v>734812</v>
       </c>
       <c r="R37" t="n">
-        <v>7088008</v>
+        <v>7088001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,32 +4242,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130043979</v>
+        <v>130068984</v>
       </c>
       <c r="B38" t="n">
-        <v>92181</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,13 +4277,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>734884</v>
+        <v>734804</v>
       </c>
       <c r="R38" t="n">
-        <v>7088266</v>
+        <v>7087973</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4452,22 +4327,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130043977</v>
+        <v>111964457</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4475,16 +4350,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4494,26 +4369,19 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Kallhögen 5, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734812</v>
+        <v>734949</v>
       </c>
       <c r="R39" t="n">
-        <v>7088001</v>
+        <v>7088268</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4537,12 +4405,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4557,22 +4435,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130068987</v>
+        <v>111965439</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4580,37 +4458,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Kallhögen 5, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735001</v>
+        <v>734926</v>
       </c>
       <c r="R40" t="n">
-        <v>7088321</v>
+        <v>7088234</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4634,12 +4513,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4654,22 +4543,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130068991</v>
+        <v>130043382</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,37 +4566,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>734748</v>
+        <v>735005</v>
       </c>
       <c r="R41" t="n">
-        <v>7088007</v>
+        <v>7088414</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4737,6 +4634,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4751,57 +4653,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130043973</v>
+        <v>130043383</v>
       </c>
       <c r="B42" t="n">
-        <v>91692</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734901</v>
+        <v>734964</v>
       </c>
       <c r="R42" t="n">
-        <v>7088302</v>
+        <v>7088319</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4836,35 +4746,39 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130068990</v>
+        <v>130043402</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4872,37 +4786,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hjåggsjö, Vb</t>
+          <t>Hjåggsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734918</v>
+        <v>734867</v>
       </c>
       <c r="R43" t="n">
-        <v>7088299</v>
+        <v>7088223</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4932,6 +4854,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre bohål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4946,15 +4873,128 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Rebecka Nygren</t>
+          <t>Elin Kannerby, Maria Wikdahl, Rebecka Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111965883</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kallhögen 5, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>734847</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7088238</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24173-2025 artfynd.xlsx
+++ b/artfynd/A 24173-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043975</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068985</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964622</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043397</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043398</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043399</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043979</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111965370</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2085,6 +2155,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964863</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043384</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,6 +2359,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043385</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043386</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043387</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2570,6 +2665,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043388</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043389</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043973</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2862,6 +2972,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043974</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2970,6 +3085,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964632</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3067,6 +3187,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043981</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3164,6 +3289,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068986</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3261,6 +3391,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068987</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3358,6 +3493,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068988</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3455,6 +3595,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068989</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3552,6 +3697,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068990</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3649,6 +3799,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068991</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3746,6 +3901,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068992</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3843,6 +4003,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043396</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3940,6 +4105,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043393</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4037,6 +4207,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043394</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4134,6 +4309,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043395</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4239,6 +4419,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043977</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4336,6 +4521,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130068984</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4444,6 +4634,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111964457</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4552,6 +4747,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111965439</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4662,6 +4862,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043382</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4772,6 +4977,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043383</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4882,6 +5092,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130043402</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4995,8 +5210,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111965883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>